--- a/astro-site/public/dl/kit-tareas-cafeteria/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas-cafeteria/05-tareas-semanales-mensuales.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Inventario Diario" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Inventario Semanal" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Limpieza Semanal" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="FIFO Semanal" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Mantenimiento Mensual" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventario Diario" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventario Semanal" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Limpieza Semanal" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FIFO Semanal" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mantenimiento Mensual" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="1" name="_xlnm.Print_Area">'Inventario Diario'!$A$1:$F$48</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'Inventario Semanal'!$A$1:$F$58</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Limpieza Semanal'!$A$1:$G$30</definedName>
-    <definedName localSheetId="4" name="_xlnm.Print_Area">'FIFO Semanal'!$A$1:$G$29</definedName>
-    <definedName localSheetId="5" name="_xlnm.Print_Area">'Mantenimiento Mensual'!$A$1:$G$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Inventario Diario'!$A$1:$F$48</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Inventario Semanal'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Inventario Semanal'!$A$1:$F$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Limpieza Semanal'!$A$1:$G$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'FIFO Semanal'!$A$1:$G$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Mantenimiento Mensual'!$A$1:$G$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -28,9 +29,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt formatCode="#,##0.00 €" numFmtId="164"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -100,6 +101,11 @@
       <color rgb="00666666"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -157,69 +163,85 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="31">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="10" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="10" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="3" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -579,15 +601,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B10"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -595,6 +618,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -602,6 +626,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -623,6 +648,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -630,8 +656,33 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-cafeteria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -645,15 +696,15 @@
   <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="30"/>
-    <col customWidth="1" max="2" min="2" width="10"/>
-    <col customWidth="1" max="3" min="3" width="10"/>
-    <col customWidth="1" max="4" min="4" width="10"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="20"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Inventario Diario de Partida — Stock Inmediato</t>
@@ -667,6 +718,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -1523,6 +1575,7 @@
       </c>
       <c r="F44" s="10" t="n"/>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
@@ -1530,6 +1583,7 @@
         </is>
       </c>
     </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" s="15" t="inlineStr">
         <is>
@@ -1542,15 +1596,15 @@
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A48:F48"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A46:F46"/>
     <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A46:F46"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A39:F39"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
@@ -1560,20 +1614,20 @@
   <sheetPr>
     <tabColor rgb="00FF6600"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="30"/>
-    <col customWidth="1" max="2" min="2" width="10"/>
-    <col customWidth="1" max="3" min="3" width="10"/>
-    <col customWidth="1" max="4" min="4" width="12"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="20"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Inventario Semanal de Almacén — Conteo por Rubros</t>
@@ -1587,6 +1641,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -2485,6 +2540,7 @@
       </c>
       <c r="F54" s="10" t="n"/>
     </row>
+    <row r="55"/>
     <row r="56">
       <c r="D56" s="20" t="inlineStr">
         <is>
@@ -2493,9 +2549,10 @@
       </c>
       <c r="E56" s="21">
         <f>SUM(E5:E54)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" s="15" t="inlineStr">
         <is>
@@ -2516,7 +2573,16 @@
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2530,16 +2596,16 @@
   <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="22" t="inlineStr">
         <is>
           <t>Limpieza Profunda Semanal</t>
@@ -2553,10 +2619,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="24" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="24" t="inlineStr">
@@ -2581,7 +2648,7 @@
       </c>
       <c r="F4" s="24" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="24" t="inlineStr">
@@ -2598,10 +2665,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="29" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
@@ -2627,10 +2692,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="30" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
@@ -2656,10 +2719,8 @@
       <c r="G7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="29" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
@@ -2685,10 +2746,8 @@
       <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="30" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
@@ -2714,10 +2773,8 @@
       <c r="G9" s="14" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="29" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
@@ -2743,10 +2800,8 @@
       <c r="G10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="30" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
@@ -2779,10 +2834,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="30" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
@@ -2808,10 +2861,8 @@
       <c r="G13" s="14" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="29" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
@@ -2837,10 +2888,8 @@
       <c r="G14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="30" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
@@ -2866,10 +2915,8 @@
       <c r="G15" s="14" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="29" t="n">
+        <v>10</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
@@ -2895,10 +2942,8 @@
       <c r="G16" s="10" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="30" t="n">
+        <v>11</v>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
@@ -2931,10 +2976,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="30" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
@@ -2960,10 +3003,8 @@
       <c r="G19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="29" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
@@ -2989,10 +3030,8 @@
       <c r="G20" s="10" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="30" t="n">
+        <v>14</v>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
@@ -3018,10 +3057,8 @@
       <c r="G21" s="14" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="29" t="n">
+        <v>15</v>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
@@ -3047,10 +3084,8 @@
       <c r="G22" s="10" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="27" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="30" t="n">
+        <v>16</v>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
@@ -3076,10 +3111,8 @@
       <c r="G23" s="14" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="29" t="n">
+        <v>17</v>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
@@ -3104,6 +3137,7 @@
       <c r="F24" s="10" t="n"/>
       <c r="G24" s="10" t="n"/>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="C26" s="20" t="inlineStr">
         <is>
@@ -3112,14 +3146,19 @@
       </c>
       <c r="D26" s="28">
         <f>COUNTIF(F5:F24,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>de 17</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F26">
+        <f>COUNTIF(B5:B24,"?*")</f>
+        <v>17.0</v>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
@@ -3127,6 +3166,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
@@ -3144,8 +3184,18 @@
     <mergeCell ref="A30:G30"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <conditionalFormatting sqref="A5:G24">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F13 F14 F15 F16 F17 F19 F20 F21 F22 F23 F24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3159,16 +3209,16 @@
   <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="22" t="inlineStr">
         <is>
           <t>Revisión FIFO Semanal — Control de Caducidades</t>
@@ -3182,10 +3232,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="24" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="24" t="inlineStr">
@@ -3210,7 +3261,7 @@
       </c>
       <c r="F4" s="24" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="24" t="inlineStr">
@@ -3227,10 +3278,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="29" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
@@ -3256,10 +3305,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="30" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
@@ -3285,10 +3332,8 @@
       <c r="G7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="29" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
@@ -3314,10 +3359,8 @@
       <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="30" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
@@ -3350,10 +3393,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="30" t="n">
+        <v>5</v>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
@@ -3379,10 +3420,8 @@
       <c r="G11" s="14" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="29" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
@@ -3408,10 +3447,8 @@
       <c r="G12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="30" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
@@ -3437,10 +3474,8 @@
       <c r="G13" s="14" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="29" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
@@ -3473,10 +3508,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="29" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
@@ -3502,10 +3535,8 @@
       <c r="G16" s="10" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="30" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
@@ -3531,10 +3562,8 @@
       <c r="G17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="29" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
@@ -3560,10 +3589,8 @@
       <c r="G18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="30" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
@@ -3596,10 +3623,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="30" t="n">
+        <v>13</v>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
@@ -3625,10 +3650,8 @@
       <c r="G21" s="14" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="29" t="n">
+        <v>14</v>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
@@ -3654,10 +3677,8 @@
       <c r="G22" s="10" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="27" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="30" t="n">
+        <v>15</v>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
@@ -3682,6 +3703,7 @@
       <c r="F23" s="14" t="n"/>
       <c r="G23" s="14" t="n"/>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="C25" s="20" t="inlineStr">
         <is>
@@ -3690,14 +3712,19 @@
       </c>
       <c r="D25" s="28">
         <f>COUNTIF(F5:F23,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E25" s="20" t="inlineStr">
         <is>
-          <t>de 15</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F25">
+        <f>COUNTIF(B5:B23,"?*")</f>
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
@@ -3705,6 +3732,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
@@ -3723,8 +3751,18 @@
     <mergeCell ref="A29:G29"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <conditionalFormatting sqref="A5:G23">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F16 F17 F18 F19 F21 F22 F23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3738,16 +3776,16 @@
   <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="22" t="inlineStr">
         <is>
           <t>Mantenimiento Mensual de Equipos</t>
@@ -3761,10 +3799,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="24" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="24" t="inlineStr">
@@ -3789,7 +3828,7 @@
       </c>
       <c r="F4" s="24" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="24" t="inlineStr">
@@ -3806,10 +3845,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="29" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
@@ -3835,10 +3872,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="30" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
@@ -3864,10 +3899,8 @@
       <c r="G7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="29" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
@@ -3893,10 +3926,8 @@
       <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="30" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
@@ -3929,10 +3960,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="30" t="n">
+        <v>5</v>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
@@ -3958,10 +3987,8 @@
       <c r="G11" s="14" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="29" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
@@ -3987,10 +4014,8 @@
       <c r="G12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="30" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
@@ -4023,10 +4048,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="30" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
@@ -4052,10 +4075,8 @@
       <c r="G15" s="14" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="29" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
@@ -4081,10 +4102,8 @@
       <c r="G16" s="10" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="30" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
@@ -4110,10 +4129,8 @@
       <c r="G17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="29" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
@@ -4139,10 +4156,8 @@
       <c r="G18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="30" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
@@ -4175,10 +4190,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="30" t="n">
+        <v>13</v>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
@@ -4204,10 +4217,8 @@
       <c r="G21" s="14" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="29" t="n">
+        <v>14</v>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
@@ -4233,10 +4244,8 @@
       <c r="G22" s="10" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="27" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="30" t="n">
+        <v>15</v>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
@@ -4261,6 +4270,7 @@
       <c r="F23" s="14" t="n"/>
       <c r="G23" s="14" t="n"/>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="C25" s="20" t="inlineStr">
         <is>
@@ -4269,14 +4279,19 @@
       </c>
       <c r="D25" s="28">
         <f>COUNTIF(F5:F23,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E25" s="20" t="inlineStr">
         <is>
-          <t>de 15</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F25">
+        <f>COUNTIF(B5:B23,"?*")</f>
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
@@ -4284,6 +4299,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
@@ -4302,7 +4318,17 @@
     <mergeCell ref="A29:G29"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <conditionalFormatting sqref="A5:G23">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F15 F16 F17 F18 F19 F21 F22 F23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-cafeteria/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas-cafeteria/05-tareas-semanales-mensuales.xlsx
@@ -15,11 +15,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mantenimiento Mensual" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Inventario Diario'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Inventario Diario'!$A$1:$F$48</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Inventario Semanal'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Inventario Semanal'!$A$1:$F$58</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Limpieza Semanal'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Limpieza Semanal'!$A$1:$G$30</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'FIFO Semanal'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'FIFO Semanal'!$A$1:$G$29</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Mantenimiento Mensual'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Mantenimiento Mensual'!$A$1:$G$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -691,7 +695,7 @@
   <sheetPr>
     <tabColor rgb="00FF6600"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1604,8 +1608,16 @@
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2591,7 +2603,7 @@
   <sheetPr>
     <tabColor rgb="00228B22"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3194,8 +3206,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -3204,7 +3224,7 @@
   <sheetPr>
     <tabColor rgb="00ED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3761,8 +3781,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -3771,7 +3799,7 @@
   <sheetPr>
     <tabColor rgb="00808080"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4328,7 +4356,15 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-cafeteria/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas-cafeteria/05-tareas-semanales-mensuales.xlsx
@@ -13,18 +13,22 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Limpieza Semanal" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FIFO Semanal" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mantenimiento Mensual" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trimestral y Anual" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Inventario Diario'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Inventario Diario'!$A$1:$F$48</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Inventario Semanal'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Inventario Semanal'!$A$1:$F$58</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Limpieza Semanal'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Limpieza Semanal'!$A$1:$G$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Limpieza Semanal'!$A$1:$G$35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'FIFO Semanal'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'FIFO Semanal'!$A$1:$G$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'FIFO Semanal'!$A$1:$G$45</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Mantenimiento Mensual'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Mantenimiento Mensual'!$A$1:$G$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Mantenimiento Mensual'!$A$1:$G$34</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Trimestral y Anual'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Trimestral y Anual'!$A$1:$G$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,7 +39,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -110,8 +114,22 @@
       <color rgb="00666666"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -142,8 +160,13 @@
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -165,11 +188,55 @@
         <color rgb="00DDDDDD"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -231,6 +298,52 @@
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -607,72 +720,192 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="31" t="inlineStr">
         <is>
           <t>Tareas Semanales, Mensuales e Inventarios — Cafetería / Brunch</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Checklists periódicos + inventarios diarios y semanales para tu cafetería.</t>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="32" t="inlineStr">
+        <is>
+          <t>Trimestral, anual y vida útil en congelación</t>
         </is>
       </c>
     </row>
     <row r="5"/>
-    <row r="6">
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>• Inventario Diario: lo hace el barista/cocinero al inicio del turno</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>• Inventario Semanal: lo hace el encargado cada lunes</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>• Limpieza, FIFO y mantenimiento: según frecuencia indicada</t>
+    <row r="6" ht="48" customHeight="1">
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>▸ La hoja «Trimestral y Anual» recoge el mantenimiento que se CONTRATA y que se pide en una inspección: DDD, conductos de extracción, extintores y BIE, instalación de gas, legionela, filtro de agua del espresso, seguro y facturación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>▸ Anota el número de parte en la columna verde y firma cuando la empresa haya venido; la última tarea de la hoja es apuntar la fecha de la próxima revisión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>▸ Al pie de «FIFO Semanal» tienes una tabla editable de vida útil en congelación por familia: una regla única para todo el congelador o tira producto bueno o valida producto pasado.</t>
         </is>
       </c>
     </row>
     <row r="9"/>
-    <row r="10">
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Formato: ☐ = tarea pendiente · ✓ = completada (escribe en columna 'Hecha')</t>
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="32" t="inlineStr">
+        <is>
+          <t>Cómo cuenta el contador</t>
         </is>
       </c>
     </row>
     <row r="11"/>
-    <row r="12">
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-cafeteria · info@aichef.pro</t>
+    <row r="12" ht="32" customHeight="1">
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>▸ Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>▸ «N/A» = no aplica en tu local: esa tarea SALE del total (no la borres, márcala N/A). «—» = no hecha: sigue contando como pendiente y baja el porcentaje, que es de lo que se trata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="B14" s="33" t="inlineStr">
+        <is>
+          <t>▸ El denominador cuenta las tareas escritas en la columna «Tarea», no un número fijo: si añades o borras tareas, el total se ajusta solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16" ht="18" customHeight="1">
+      <c r="B16" s="32" t="inlineStr">
+        <is>
+          <t>Filas libres</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18" ht="32" customHeight="1">
+      <c r="B18" s="33" t="inlineStr">
+        <is>
+          <t>▸ Al final de cada tabla hay 5 filas verdes libres DENTRO del rango que cuenta el contador: escribe ahí tus tareas propias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="B19" s="33" t="inlineStr">
+        <is>
+          <t>▸ Si necesitas más, inserta filas DENTRO de la tabla (clic derecho → Insertar), nunca por debajo de la última: lo que se escriba fuera del rango no lo cuenta nadie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="B21" s="32" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>▸ Las hojas con fórmulas van protegidas SIN contraseña: las celdas de entrada (las verdes) están desbloqueadas y los cálculos no se pisan por accidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>▸ Puedes insertar y borrar filas con la protección puesta. Para cambiar la estructura: Revisar → Desproteger hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="B26" s="32" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="B28" s="33" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="B29" s="33" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (cocina, sala, barra café).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="B31" s="33" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="B32" s="33" t="inlineStr">
+        <is>
+          <t>▸ Estás en 05-tareas-semanales-mensuales.xlsx: lo que NO es diario (semanal, mensual, trimestral y anual). El día a día está en 08-apertura-cierre-negocio.xlsx y 01-apertura-cierre.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="32" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Cafetería / Brunch · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="35" customHeight="1">
+      <c r="B36" s="32" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="B37" s="32" t="inlineStr">
+        <is>
+          <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="B39" s="32" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-cafeteria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1812,6 @@
       </c>
       <c r="F44" s="10" t="n"/>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
@@ -1587,7 +1819,6 @@
         </is>
       </c>
     </row>
-    <row r="47"/>
     <row r="48">
       <c r="A48" s="15" t="inlineStr">
         <is>
@@ -2552,7 +2783,6 @@
       </c>
       <c r="F54" s="10" t="n"/>
     </row>
-    <row r="55"/>
     <row r="56">
       <c r="D56" s="20" t="inlineStr">
         <is>
@@ -2564,7 +2794,6 @@
         <v>0.0</v>
       </c>
     </row>
-    <row r="57"/>
     <row r="58">
       <c r="A58" s="15" t="inlineStr">
         <is>
@@ -2605,7 +2834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2627,7 +2856,7 @@
     <row r="2">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable: ________________</t>
+          <t>Semana del ___/___/______ al ___/___/______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2884,7 @@
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Día</t>
         </is>
       </c>
       <c r="F4" s="24" t="inlineStr">
@@ -2670,539 +2899,604 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  COCINA</t>
         </is>
       </c>
+      <c r="B5" s="35" t="n"/>
+      <c r="C5" s="35" t="n"/>
+      <c r="D5" s="35" t="n"/>
+      <c r="E5" s="35" t="n"/>
+      <c r="F5" s="35" t="n"/>
+      <c r="G5" s="35" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="n">
+      <c r="A6" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>Limpiar interior de cámaras frigoríficas</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="38" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
+      <c r="F6" s="39" t="n"/>
+      <c r="G6" s="39" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="n">
+      <c r="A7" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="41" t="inlineStr">
         <is>
           <t>Desmontar y limpiar campana extractora</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="38" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
+      <c r="F7" s="39" t="n"/>
+      <c r="G7" s="39" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="n">
+      <c r="A8" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>Limpiar interior de horno a fondo</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="38" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
+      <c r="F8" s="39" t="n"/>
+      <c r="G8" s="39" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="n">
+      <c r="A9" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="41" t="inlineStr">
         <is>
           <t>Limpiar detrás y debajo de equipos</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="38" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
+      <c r="F9" s="39" t="n"/>
+      <c r="G9" s="39" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="n">
+      <c r="A10" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="37" t="inlineStr">
         <is>
           <t>Desinfectar tablas de corte (sumergir en lejía)</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="38" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
+      <c r="F10" s="39" t="n"/>
+      <c r="G10" s="39" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="n">
+      <c r="A11" s="40" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="41" t="inlineStr">
         <is>
           <t>Limpiar estanterías de almacén</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="38" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
+      <c r="F11" s="39" t="n"/>
+      <c r="G11" s="39" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  BARRA</t>
         </is>
       </c>
+      <c r="B12" s="35" t="n"/>
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="35" t="n"/>
+      <c r="E12" s="35" t="n"/>
+      <c r="F12" s="35" t="n"/>
+      <c r="G12" s="35" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="n">
+      <c r="A13" s="40" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="41" t="inlineStr">
         <is>
           <t>Limpiar interior de vitrina a fondo</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="38" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="38" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
+      <c r="F13" s="39" t="n"/>
+      <c r="G13" s="39" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="n">
+      <c r="A14" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="37" t="inlineStr">
         <is>
           <t>Limpiar grupo de espresso con cepillo especial</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="38" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="38" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
+      <c r="F14" s="39" t="n"/>
+      <c r="G14" s="39" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="30" t="n">
+      <c r="A15" s="40" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="41" t="inlineStr">
         <is>
           <t>Limpiar molinillo interior (sin agua)</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="38" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="38" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
+      <c r="F15" s="39" t="n"/>
+      <c r="G15" s="39" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="29" t="n">
+      <c r="A16" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="37" t="inlineStr">
         <is>
           <t>Limpiar nevera de barra interior</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="38" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="38" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
+      <c r="F16" s="39" t="n"/>
+      <c r="G16" s="39" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="30" t="n">
+      <c r="A17" s="40" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="41" t="inlineStr">
         <is>
           <t>Desinfectar superficie de barra completa</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="38" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="38" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
+      <c r="F17" s="39" t="n"/>
+      <c r="G17" s="39" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  SALA Y BAÑOS</t>
         </is>
       </c>
+      <c r="B18" s="35" t="n"/>
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="35" t="n"/>
+      <c r="E18" s="35" t="n"/>
+      <c r="F18" s="35" t="n"/>
+      <c r="G18" s="35" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="n">
+      <c r="A19" s="40" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>Limpiar cristales interiores y exteriores</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="38" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="38" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="14" t="n"/>
+      <c r="F19" s="39" t="n"/>
+      <c r="G19" s="39" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="n">
+      <c r="A20" s="36" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="37" t="inlineStr">
         <is>
           <t>Limpiar sillas y bancos a fondo</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="38" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D20" s="38" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
+      <c r="F20" s="39" t="n"/>
+      <c r="G20" s="39" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="30" t="n">
+      <c r="A21" s="40" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="41" t="inlineStr">
         <is>
           <t>Fregar suelos con producto desengrasante</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C21" s="38" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="38" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="14" t="n"/>
+      <c r="F21" s="39" t="n"/>
+      <c r="G21" s="39" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="29" t="n">
+      <c r="A22" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="37" t="inlineStr">
         <is>
           <t>Limpieza profunda de baños: azulejos, espejos, suelo</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="38" t="inlineStr">
         <is>
           <t>Baños</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="38" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
+      <c r="F22" s="39" t="n"/>
+      <c r="G22" s="39" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="30" t="n">
+      <c r="A23" s="40" t="n">
         <v>16</v>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="41" t="inlineStr">
         <is>
           <t>Limpiar terraza a fondo (si aplica)</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C23" s="38" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="38" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="14" t="n"/>
+      <c r="F23" s="39" t="n"/>
+      <c r="G23" s="39" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="29" t="n">
+      <c r="A24" s="36" t="n">
         <v>17</v>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="37" t="inlineStr">
         <is>
           <t>Revisar y reponer productos de limpieza</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="38" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D24" s="38" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="10" t="n"/>
-    </row>
-    <row r="25"/>
+      <c r="F24" s="39" t="n"/>
+      <c r="G24" s="39" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="42" t="n"/>
+      <c r="B25" s="43" t="n"/>
+      <c r="C25" s="38" t="n"/>
+      <c r="D25" s="38" t="n"/>
+      <c r="E25" s="38" t="n"/>
+      <c r="F25" s="39" t="n"/>
+      <c r="G25" s="39" t="n"/>
+    </row>
     <row r="26">
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D26" s="28">
-        <f>COUNTIF(F5:F24,"✓")</f>
+      <c r="A26" s="42" t="n"/>
+      <c r="B26" s="43" t="n"/>
+      <c r="C26" s="38" t="n"/>
+      <c r="D26" s="38" t="n"/>
+      <c r="E26" s="38" t="n"/>
+      <c r="F26" s="39" t="n"/>
+      <c r="G26" s="39" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="42" t="n"/>
+      <c r="B27" s="43" t="n"/>
+      <c r="C27" s="38" t="n"/>
+      <c r="D27" s="38" t="n"/>
+      <c r="E27" s="38" t="n"/>
+      <c r="F27" s="39" t="n"/>
+      <c r="G27" s="39" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="42" t="n"/>
+      <c r="B28" s="43" t="n"/>
+      <c r="C28" s="38" t="n"/>
+      <c r="D28" s="38" t="n"/>
+      <c r="E28" s="38" t="n"/>
+      <c r="F28" s="39" t="n"/>
+      <c r="G28" s="39" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="42" t="n"/>
+      <c r="B29" s="43" t="n"/>
+      <c r="C29" s="38" t="n"/>
+      <c r="D29" s="38" t="n"/>
+      <c r="E29" s="38" t="n"/>
+      <c r="F29" s="39" t="n"/>
+      <c r="G29" s="39" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D31" s="28">
+        <f>COUNTIFS(B5:B29,"?*",F5:F29,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E26" s="20" t="inlineStr">
+      <c r="E31" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F26">
-        <f>COUNTIF(B5:B24,"?*")</f>
+      <c r="F31">
+        <f>COUNTIF(B5:B29,"?*")-COUNTIF(F5:F29,"N/A")</f>
         <v>17.0</v>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Cafetería / Brunch · AI Chef Pro · aichef.pro —</t>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Cafetería / Brunch · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="8">
     <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A33:G33"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A31:C31"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G24">
+  <conditionalFormatting sqref="A5:G29">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F13 F14 F15 F16 F17 F19 F20 F21 F22 F23 F24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F13 F14 F15 F16 F17 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3226,7 +3520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3248,7 +3542,7 @@
     <row r="2">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable: ________________</t>
+          <t>Semana del ___/___/______ al ___/___/______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3570,7 @@
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Día</t>
         </is>
       </c>
       <c r="F4" s="24" t="inlineStr">
@@ -3291,493 +3585,771 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  CÁMARAS FRIGORÍFICAS</t>
         </is>
       </c>
+      <c r="B5" s="35" t="n"/>
+      <c r="C5" s="35" t="n"/>
+      <c r="D5" s="35" t="n"/>
+      <c r="E5" s="35" t="n"/>
+      <c r="F5" s="35" t="n"/>
+      <c r="G5" s="35" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="n">
+      <c r="A6" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>Verificar etiquetado y fechas de todos los productos abiertos</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="38" t="inlineStr">
         <is>
           <t>Cámara</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="38" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
+      <c r="F6" s="39" t="n"/>
+      <c r="G6" s="39" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="n">
+      <c r="A7" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="41" t="inlineStr">
         <is>
           <t>Rotar: producto más antiguo delante</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="38" t="inlineStr">
         <is>
           <t>Cámara</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="38" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
+      <c r="F7" s="39" t="n"/>
+      <c r="G7" s="39" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="n">
+      <c r="A8" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>Desechar producto caducado o en mal estado</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="38" t="inlineStr">
         <is>
           <t>Cámara</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="38" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
+      <c r="F8" s="39" t="n"/>
+      <c r="G8" s="39" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="n">
+      <c r="A9" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>Verificar temperaturas de todas las cámaras</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="B9" s="41" t="inlineStr">
+        <is>
+          <t>Verificar temperaturas de todas las cámaras (refrigeración 0-4 °C) — anota la lectura: ____ °C</t>
+        </is>
+      </c>
+      <c r="C9" s="38" t="inlineStr">
         <is>
           <t>Cámara</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="38" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
+      <c r="F9" s="39" t="n"/>
+      <c r="G9" s="39" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  BARRA Y VITRINA</t>
         </is>
       </c>
+      <c r="B10" s="35" t="n"/>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="35" t="n"/>
+      <c r="E10" s="35" t="n"/>
+      <c r="F10" s="35" t="n"/>
+      <c r="G10" s="35" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="n">
+      <c r="A11" s="40" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="41" t="inlineStr">
         <is>
           <t>Revisar caducidad de leches abiertas</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="38" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
+      <c r="F11" s="39" t="n"/>
+      <c r="G11" s="39" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="n">
+      <c r="A12" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>Revisar caducidad de siropes abiertos</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="38" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="38" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
+      <c r="F12" s="39" t="n"/>
+      <c r="G12" s="39" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="n">
+      <c r="A13" s="40" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="41" t="inlineStr">
         <is>
           <t>Verificar estado de bollería (frescura)</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="38" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="38" t="inlineStr">
         <is>
           <t>Pastelero/a</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
+      <c r="F13" s="39" t="n"/>
+      <c r="G13" s="39" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="n">
+      <c r="A14" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="37" t="inlineStr">
         <is>
           <t>Revisar caducidad de zumos</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="38" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="38" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
+      <c r="F14" s="39" t="n"/>
+      <c r="G14" s="39" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  ALMACÉN SECO</t>
         </is>
       </c>
+      <c r="B15" s="35" t="n"/>
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="35" t="n"/>
+      <c r="E15" s="35" t="n"/>
+      <c r="F15" s="35" t="n"/>
+      <c r="G15" s="35" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="29" t="n">
+      <c r="A16" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="37" t="inlineStr">
         <is>
           <t>Revisar caducidad de café en grano (frescura)</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="38" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="38" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
+      <c r="F16" s="39" t="n"/>
+      <c r="G16" s="39" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="30" t="n">
+      <c r="A17" s="40" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="41" t="inlineStr">
         <is>
           <t>Revisar caducidad de tés e infusiones</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="38" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="38" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
+      <c r="F17" s="39" t="n"/>
+      <c r="G17" s="39" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="n">
+      <c r="A18" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>Revisar stock de packaging: vasos, tapas, bolsas</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="38" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="38" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
+      <c r="F18" s="39" t="n"/>
+      <c r="G18" s="39" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="n">
+      <c r="A19" s="40" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>Verificar que no hay plagas ni humedad</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="38" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="38" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="14" t="n"/>
+      <c r="F19" s="39" t="n"/>
+      <c r="G19" s="39" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  FRESCOS</t>
         </is>
       </c>
+      <c r="B20" s="35" t="n"/>
+      <c r="C20" s="35" t="n"/>
+      <c r="D20" s="35" t="n"/>
+      <c r="E20" s="35" t="n"/>
+      <c r="F20" s="35" t="n"/>
+      <c r="G20" s="35" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="30" t="n">
+      <c r="A21" s="40" t="n">
         <v>13</v>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="41" t="inlineStr">
         <is>
           <t>Revisar fruta fresca: desechar lo pasado</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C21" s="38" t="inlineStr">
         <is>
           <t>Cámara</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="38" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="14" t="n"/>
+      <c r="F21" s="39" t="n"/>
+      <c r="G21" s="39" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="29" t="n">
+      <c r="A22" s="36" t="n">
         <v>14</v>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="37" t="inlineStr">
         <is>
           <t>Revisar huevos: fecha de caducidad</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="38" t="inlineStr">
         <is>
           <t>Cámara</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="38" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
+      <c r="F22" s="39" t="n"/>
+      <c r="G22" s="39" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="30" t="n">
+      <c r="A23" s="40" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>Revisar pan: congelar lo que no se usará</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="B23" s="41" t="inlineStr">
+        <is>
+          <t>Revisar el pan y la bollería: congelar EN EL DÍA lo que no se usará y etiquetar con la fecha (vida útil por familia en la tabla del pie de esta hoja)</t>
+        </is>
+      </c>
+      <c r="C23" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="38" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="38" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="14" t="n"/>
-    </row>
-    <row r="24"/>
+      <c r="F23" s="39" t="n"/>
+      <c r="G23" s="39" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="42" t="n"/>
+      <c r="B24" s="43" t="n"/>
+      <c r="C24" s="38" t="n"/>
+      <c r="D24" s="38" t="n"/>
+      <c r="E24" s="38" t="n"/>
+      <c r="F24" s="39" t="n"/>
+      <c r="G24" s="39" t="n"/>
+    </row>
     <row r="25">
-      <c r="C25" s="20" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D25" s="28">
-        <f>COUNTIF(F5:F23,"✓")</f>
+      <c r="A25" s="42" t="n"/>
+      <c r="B25" s="43" t="n"/>
+      <c r="C25" s="38" t="n"/>
+      <c r="D25" s="38" t="n"/>
+      <c r="E25" s="38" t="n"/>
+      <c r="F25" s="39" t="n"/>
+      <c r="G25" s="39" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="42" t="n"/>
+      <c r="B26" s="43" t="n"/>
+      <c r="C26" s="38" t="n"/>
+      <c r="D26" s="38" t="n"/>
+      <c r="E26" s="38" t="n"/>
+      <c r="F26" s="39" t="n"/>
+      <c r="G26" s="39" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="42" t="n"/>
+      <c r="B27" s="43" t="n"/>
+      <c r="C27" s="38" t="n"/>
+      <c r="D27" s="38" t="n"/>
+      <c r="E27" s="38" t="n"/>
+      <c r="F27" s="39" t="n"/>
+      <c r="G27" s="39" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="42" t="n"/>
+      <c r="B28" s="43" t="n"/>
+      <c r="C28" s="38" t="n"/>
+      <c r="D28" s="38" t="n"/>
+      <c r="E28" s="38" t="n"/>
+      <c r="F28" s="39" t="n"/>
+      <c r="G28" s="39" t="n"/>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D30" s="28">
+        <f>COUNTIFS(B5:B28,"?*",F5:F28,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F25">
-        <f>COUNTIF(B5:B23,"?*")</f>
+      <c r="F30">
+        <f>COUNTIF(B5:B28,"?*")-COUNTIF(F5:F28,"N/A")</f>
         <v>15.0</v>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Cafetería / Brunch · AI Chef Pro · aichef.pro —</t>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>VIDA ÚTIL ORIENTATIVA EN CONGELACIÓN A −18 °C — ajústala a tu producto y a tu proveedor</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="n"/>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>Familia</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>Vida útil</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+      <c r="E35" s="44" t="n"/>
+      <c r="F35" s="44" t="n"/>
+      <c r="G35" s="45" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="30" t="n"/>
+      <c r="B36" s="43" t="inlineStr">
+        <is>
+          <t>Croissants y masas de bollería crudas</t>
+        </is>
+      </c>
+      <c r="C36" s="38" t="inlineStr">
+        <is>
+          <t>1-2 meses</t>
+        </is>
+      </c>
+      <c r="D36" s="38" t="inlineStr">
+        <is>
+          <t>La levadura pierde fuerza: después sube mal aunque sea seguro comerlo</t>
+        </is>
+      </c>
+      <c r="E36" s="44" t="n"/>
+      <c r="F36" s="44" t="n"/>
+      <c r="G36" s="45" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="30" t="n"/>
+      <c r="B37" s="43" t="inlineStr">
+        <is>
+          <t>Pan y bollería ya horneada</t>
+        </is>
+      </c>
+      <c r="C37" s="38" t="inlineStr">
+        <is>
+          <t>1-3 meses</t>
+        </is>
+      </c>
+      <c r="D37" s="38" t="inlineStr">
+        <is>
+          <t>Pierde textura antes que seguridad; descongela y regenera en horno</t>
+        </is>
+      </c>
+      <c r="E37" s="44" t="n"/>
+      <c r="F37" s="44" t="n"/>
+      <c r="G37" s="45" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="30" t="n"/>
+      <c r="B38" s="43" t="inlineStr">
+        <is>
+          <t>Tartas y bizcochos sin nata montada</t>
+        </is>
+      </c>
+      <c r="C38" s="38" t="inlineStr">
+        <is>
+          <t>2-3 meses</t>
+        </is>
+      </c>
+      <c r="D38" s="38" t="inlineStr">
+        <is>
+          <t>La nata montada y las cremas de huevo NO aguantan la congelación</t>
+        </is>
+      </c>
+      <c r="E38" s="44" t="n"/>
+      <c r="F38" s="44" t="n"/>
+      <c r="G38" s="45" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="30" t="n"/>
+      <c r="B39" s="43" t="inlineStr">
+        <is>
+          <t>Salmón ahumado y pescado azul</t>
+        </is>
+      </c>
+      <c r="C39" s="38" t="inlineStr">
+        <is>
+          <t>2-3 meses</t>
+        </is>
+      </c>
+      <c r="D39" s="38" t="inlineStr">
+        <is>
+          <t>La grasa se enrancia aunque esté congelado: es el que antes se estropea</t>
+        </is>
+      </c>
+      <c r="E39" s="44" t="n"/>
+      <c r="F39" s="44" t="n"/>
+      <c r="G39" s="45" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="30" t="n"/>
+      <c r="B40" s="43" t="inlineStr">
+        <is>
+          <t>Bacon, jamón y embutido loncheado</t>
+        </is>
+      </c>
+      <c r="C40" s="38" t="inlineStr">
+        <is>
+          <t>1-2 meses</t>
+        </is>
+      </c>
+      <c r="D40" s="38" t="inlineStr">
+        <is>
+          <t>La sal acelera el enranciamiento de la grasa</t>
+        </is>
+      </c>
+      <c r="E40" s="44" t="n"/>
+      <c r="F40" s="44" t="n"/>
+      <c r="G40" s="45" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="30" t="n"/>
+      <c r="B41" s="43" t="inlineStr">
+        <is>
+          <t>Fruta troceada y pulpas para bowls</t>
+        </is>
+      </c>
+      <c r="C41" s="38" t="inlineStr">
+        <is>
+          <t>8-12 meses</t>
+        </is>
+      </c>
+      <c r="D41" s="38" t="inlineStr">
+        <is>
+          <t>Congélala el mismo día del corte y en porciones de un solo uso</t>
+        </is>
+      </c>
+      <c r="E41" s="44" t="n"/>
+      <c r="F41" s="44" t="n"/>
+      <c r="G41" s="45" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="30" t="n"/>
+      <c r="B42" s="43" t="inlineStr">
+        <is>
+          <t>Caldos, cremas y salsas propias</t>
+        </is>
+      </c>
+      <c r="C42" s="38" t="inlineStr">
+        <is>
+          <t>3 meses</t>
+        </is>
+      </c>
+      <c r="D42" s="38" t="inlineStr">
+        <is>
+          <t>Etiquetar con fecha de producción Y de congelación: la vida útil de esta tabla se cuenta desde la de congelación</t>
+        </is>
+      </c>
+      <c r="E42" s="44" t="n"/>
+      <c r="F42" s="44" t="n"/>
+      <c r="G42" s="45" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="30" t="n"/>
+      <c r="B43" s="43" t="inlineStr">
+        <is>
+          <t>Café en grano</t>
+        </is>
+      </c>
+      <c r="C43" s="38" t="inlineStr">
+        <is>
+          <t>No congelar</t>
+        </is>
+      </c>
+      <c r="D43" s="38" t="inlineStr">
+        <is>
+          <t>Para uso diario no se congela: la condensación de abrir y cerrar la bolsa arruina el grano</t>
+        </is>
+      </c>
+      <c r="E43" s="44" t="n"/>
+      <c r="F43" s="44" t="n"/>
+      <c r="G43" s="45" t="n"/>
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Cafetería / Brunch · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="19">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="D38:G38"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="D41:G41"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="D36:G36"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="D40:G40"/>
+    <mergeCell ref="D37:G37"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="D42:G42"/>
+    <mergeCell ref="D39:G39"/>
+    <mergeCell ref="D43:G43"/>
+    <mergeCell ref="A45:G45"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G23">
+  <conditionalFormatting sqref="A5:G28">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F16 F17 F18 F19 F21 F22 F23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F16 F17 F18 F19 F21 F22 F23 F24 F25 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3801,7 +4373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3823,7 +4395,7 @@
     <row r="2">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable: ________________</t>
+          <t>Mes: ________________   Año: ______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -3851,7 +4423,7 @@
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cadencia</t>
         </is>
       </c>
       <c r="F4" s="24" t="inlineStr">
@@ -3866,493 +4438,1150 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  MÁQUINA DE ESPRESSO</t>
         </is>
       </c>
+      <c r="B5" s="35" t="n"/>
+      <c r="C5" s="35" t="n"/>
+      <c r="D5" s="35" t="n"/>
+      <c r="E5" s="35" t="n"/>
+      <c r="F5" s="35" t="n"/>
+      <c r="G5" s="35" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="n">
+      <c r="A6" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>Descalcificar máquina de espresso completa</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="38" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="38" t="inlineStr">
         <is>
           <t>Técnico/Barista</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="38" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
+      <c r="F6" s="39" t="n"/>
+      <c r="G6" s="39" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="n">
+      <c r="A7" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="41" t="inlineStr">
         <is>
           <t>Cambiar juntas de grupo si están desgastadas</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="38" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="38" t="inlineStr">
         <is>
           <t>Técnico</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="38" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
+      <c r="F7" s="39" t="n"/>
+      <c r="G7" s="39" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="n">
+      <c r="A8" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>Verificar presión de caldera</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="38" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="38" t="inlineStr">
         <is>
           <t>Técnico</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="38" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
+      <c r="F8" s="39" t="n"/>
+      <c r="G8" s="39" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="n">
+      <c r="A9" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="41" t="inlineStr">
         <is>
           <t>Limpiar filtro de agua</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="38" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="38" t="inlineStr">
         <is>
           <t>Técnico</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="38" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
+      <c r="F9" s="39" t="n"/>
+      <c r="G9" s="39" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOLINILLO</t>
         </is>
       </c>
+      <c r="B10" s="35" t="n"/>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="35" t="n"/>
+      <c r="E10" s="35" t="n"/>
+      <c r="F10" s="35" t="n"/>
+      <c r="G10" s="35" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="n">
+      <c r="A11" s="40" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="41" t="inlineStr">
         <is>
           <t>Limpiar muelas del molinillo a fondo</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="38" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="38" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
+      <c r="F11" s="39" t="n"/>
+      <c r="G11" s="39" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="n">
+      <c r="A12" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>Verificar desgaste de muelas (cambiar si aplica)</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="38" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="38" t="inlineStr">
         <is>
           <t>Técnico</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="38" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
+      <c r="F12" s="39" t="n"/>
+      <c r="G12" s="39" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="n">
+      <c r="A13" s="40" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="41" t="inlineStr">
         <is>
           <t>Calibrar dosificación</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="38" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="38" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="38" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
+      <c r="F13" s="39" t="n"/>
+      <c r="G13" s="39" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  COCINA Y GENERAL</t>
         </is>
       </c>
+      <c r="B14" s="35" t="n"/>
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="35" t="n"/>
+      <c r="E14" s="35" t="n"/>
+      <c r="F14" s="35" t="n"/>
+      <c r="G14" s="35" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="30" t="n">
+      <c r="A15" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="41" t="inlineStr">
         <is>
           <t>Revisión horno: resistencias, puerta, juntas</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="38" t="inlineStr">
         <is>
           <t>Técnico</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="38" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
+      <c r="F15" s="39" t="n"/>
+      <c r="G15" s="39" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="29" t="n">
+      <c r="A16" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="37" t="inlineStr">
         <is>
           <t>Lavavajillas: limpiar filtros, verificar abrillantador y sal</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="38" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="38" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
+      <c r="F16" s="39" t="n"/>
+      <c r="G16" s="39" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="30" t="n">
+      <c r="A17" s="40" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="41" t="inlineStr">
         <is>
           <t>Revisar campana extractora y filtros</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="38" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="38" t="inlineStr">
         <is>
           <t>Técnico</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="38" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
+      <c r="F17" s="39" t="n"/>
+      <c r="G17" s="39" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="n">
+      <c r="A18" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>Revisar climatización: filtros, temperatura</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="38" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="38" t="inlineStr">
         <is>
           <t>Técnico</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="38" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
+      <c r="F18" s="39" t="n"/>
+      <c r="G18" s="39" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="n">
+      <c r="A19" s="40" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>Verificar estado de instalación eléctrica</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="38" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="38" t="inlineStr">
         <is>
           <t>Técnico</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="38" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="14" t="n"/>
+      <c r="F19" s="39" t="n"/>
+      <c r="G19" s="39" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  SEGURIDAD Y CUMPLIMIENTO</t>
         </is>
       </c>
+      <c r="B20" s="35" t="n"/>
+      <c r="C20" s="35" t="n"/>
+      <c r="D20" s="35" t="n"/>
+      <c r="E20" s="35" t="n"/>
+      <c r="F20" s="35" t="n"/>
+      <c r="G20" s="35" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="30" t="n">
+      <c r="A21" s="40" t="n">
         <v>13</v>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="41" t="inlineStr">
         <is>
           <t>Verificar extintor: presión, caducidad, accesibilidad</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C21" s="38" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="38" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="38" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="14" t="n"/>
+      <c r="F21" s="39" t="n"/>
+      <c r="G21" s="39" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="29" t="n">
+      <c r="A22" s="36" t="n">
         <v>14</v>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="37" t="inlineStr">
         <is>
           <t>Verificar botiquín: stock completo, caducidades</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="38" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="38" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="38" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
+      <c r="F22" s="39" t="n"/>
+      <c r="G22" s="39" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="30" t="n">
+      <c r="A23" s="40" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="41" t="inlineStr">
         <is>
           <t>Revisar salidas de emergencia: despejadas y señalizadas</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C23" s="38" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="38" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="38" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="14" t="n"/>
-    </row>
-    <row r="24"/>
+      <c r="F23" s="39" t="n"/>
+      <c r="G23" s="39" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="42" t="n"/>
+      <c r="B24" s="43" t="n"/>
+      <c r="C24" s="38" t="n"/>
+      <c r="D24" s="38" t="n"/>
+      <c r="E24" s="38" t="n"/>
+      <c r="F24" s="39" t="n"/>
+      <c r="G24" s="39" t="n"/>
+    </row>
     <row r="25">
-      <c r="C25" s="20" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D25" s="28">
-        <f>COUNTIF(F5:F23,"✓")</f>
+      <c r="A25" s="42" t="n"/>
+      <c r="B25" s="43" t="n"/>
+      <c r="C25" s="38" t="n"/>
+      <c r="D25" s="38" t="n"/>
+      <c r="E25" s="38" t="n"/>
+      <c r="F25" s="39" t="n"/>
+      <c r="G25" s="39" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="42" t="n"/>
+      <c r="B26" s="43" t="n"/>
+      <c r="C26" s="38" t="n"/>
+      <c r="D26" s="38" t="n"/>
+      <c r="E26" s="38" t="n"/>
+      <c r="F26" s="39" t="n"/>
+      <c r="G26" s="39" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="42" t="n"/>
+      <c r="B27" s="43" t="n"/>
+      <c r="C27" s="38" t="n"/>
+      <c r="D27" s="38" t="n"/>
+      <c r="E27" s="38" t="n"/>
+      <c r="F27" s="39" t="n"/>
+      <c r="G27" s="39" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="42" t="n"/>
+      <c r="B28" s="43" t="n"/>
+      <c r="C28" s="38" t="n"/>
+      <c r="D28" s="38" t="n"/>
+      <c r="E28" s="38" t="n"/>
+      <c r="F28" s="39" t="n"/>
+      <c r="G28" s="39" t="n"/>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D30" s="28">
+        <f>COUNTIFS(B5:B28,"?*",F5:F28,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F25">
-        <f>COUNTIF(B5:B23,"?*")</f>
+      <c r="F30">
+        <f>COUNTIF(B5:B28,"?*")-COUNTIF(F5:F28,"N/A")</f>
         <v>15.0</v>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Cafetería / Brunch · AI Chef Pro · aichef.pro —</t>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Cafetería / Brunch · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="9">
     <mergeCell ref="A20:G20"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A30:C30"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A29:G29"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G23">
+  <conditionalFormatting sqref="A5:G28">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F15 F16 F17 F18 F19 F21 F22 F23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F15 F16 F17 F18 F19 F21 F22 F23 F24 F25 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00808080"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>Mantenimiento Trimestral y Anual — Revisiones Contratadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>Mes: ________________   Año: ______    Responsable: _________________________</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>Nº</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>Nº de parte</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>Cadencia</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>✓ Completada</t>
+        </is>
+      </c>
+      <c r="G4" s="24" t="inlineStr">
+        <is>
+          <t>Firma</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CONTRATADO — EMPRESA AUTORIZADA</t>
+        </is>
+      </c>
+      <c r="B5" s="35" t="n"/>
+      <c r="C5" s="35" t="n"/>
+      <c r="D5" s="35" t="n"/>
+      <c r="E5" s="35" t="n"/>
+      <c r="F5" s="35" t="n"/>
+      <c r="G5" s="35" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="37" t="inlineStr">
+        <is>
+          <t>Control de plagas (DDD): visita de la empresa autorizada, parte firmado y certificado en vigor</t>
+        </is>
+      </c>
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="38" t="inlineStr">
+        <is>
+          <t>Empresa DDD</t>
+        </is>
+      </c>
+      <c r="E6" s="38" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="F6" s="39" t="n"/>
+      <c r="G6" s="39" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="41" t="inlineStr">
+        <is>
+          <t>Limpieza de campana y conductos de extracción por empresa homologada</t>
+        </is>
+      </c>
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="38" t="inlineStr">
+        <is>
+          <t>Empresa externa</t>
+        </is>
+      </c>
+      <c r="E7" s="38" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F7" s="39" t="n"/>
+      <c r="G7" s="39" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="37" t="inlineStr">
+        <is>
+          <t>Revisión de extintores y BIE por empresa mantenedora (etiqueta y acta de revisión)</t>
+        </is>
+      </c>
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="38" t="inlineStr">
+        <is>
+          <t>Mantenedor</t>
+        </is>
+      </c>
+      <c r="E8" s="38" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F8" s="39" t="n"/>
+      <c r="G8" s="39" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="41" t="inlineStr">
+        <is>
+          <t>Prevención de legionela si hay torre de refrigeración o agua caliente sanitaria de riesgo</t>
+        </is>
+      </c>
+      <c r="C9" s="38" t="n"/>
+      <c r="D9" s="38" t="inlineStr">
+        <is>
+          <t>Empresa autorizada</t>
+        </is>
+      </c>
+      <c r="E9" s="38" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F9" s="39" t="n"/>
+      <c r="G9" s="39" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GAS, FRÍO Y RESIDUOS</t>
+        </is>
+      </c>
+      <c r="B10" s="35" t="n"/>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="35" t="n"/>
+      <c r="E10" s="35" t="n"/>
+      <c r="F10" s="35" t="n"/>
+      <c r="G10" s="35" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="41" t="inlineStr">
+        <is>
+          <t>Revisión periódica de la instalación de gas por empresa habilitada, si el local tiene gas</t>
+        </is>
+      </c>
+      <c r="C11" s="38" t="n"/>
+      <c r="D11" s="38" t="inlineStr">
+        <is>
+          <t>Instalador gas</t>
+        </is>
+      </c>
+      <c r="E11" s="38" t="inlineStr">
+        <is>
+          <t>Cada 5 años</t>
+        </is>
+      </c>
+      <c r="F11" s="39" t="n"/>
+      <c r="G11" s="39" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="37" t="inlineStr">
+        <is>
+          <t>Revisión de cámaras y vitrinas refrigeradas por frigorista: estanqueidad y gas refrigerante</t>
+        </is>
+      </c>
+      <c r="C12" s="38" t="n"/>
+      <c r="D12" s="38" t="inlineStr">
+        <is>
+          <t>Frigorista</t>
+        </is>
+      </c>
+      <c r="E12" s="38" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F12" s="39" t="n"/>
+      <c r="G12" s="39" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="41" t="inlineStr">
+        <is>
+          <t>Retirada del aceite usado por gestor autorizado y archivo del documento de entrega, si hay freidora</t>
+        </is>
+      </c>
+      <c r="C13" s="38" t="n"/>
+      <c r="D13" s="38" t="inlineStr">
+        <is>
+          <t>Gestor autorizado</t>
+        </is>
+      </c>
+      <c r="E13" s="38" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="F13" s="39" t="n"/>
+      <c r="G13" s="39" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AGUA Y EQUIPOS DE CAFÉ</t>
+        </is>
+      </c>
+      <c r="B14" s="35" t="n"/>
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="35" t="n"/>
+      <c r="E14" s="35" t="n"/>
+      <c r="F14" s="35" t="n"/>
+      <c r="G14" s="35" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="41" t="inlineStr">
+        <is>
+          <t>Cambiar el filtro descalcificador de agua de la máquina de espresso y anotar la fecha del cambio</t>
+        </is>
+      </c>
+      <c r="C15" s="38" t="n"/>
+      <c r="D15" s="38" t="inlineStr">
+        <is>
+          <t>Técnico SAT</t>
+        </is>
+      </c>
+      <c r="E15" s="38" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="F15" s="39" t="n"/>
+      <c r="G15" s="39" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="37" t="inlineStr">
+        <is>
+          <t>Medir la dureza del agua (GH/KH) y ajustar el filtro: el agua es casi todo lo que hay en la taza</t>
+        </is>
+      </c>
+      <c r="C16" s="38" t="n"/>
+      <c r="D16" s="38" t="inlineStr">
+        <is>
+          <t>Barista</t>
+        </is>
+      </c>
+      <c r="E16" s="38" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="F16" s="39" t="n"/>
+      <c r="G16" s="39" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="41" t="inlineStr">
+        <is>
+          <t>Revisión técnica completa de la máquina de espresso por el SAT: juntas, presión y válvula de seguridad</t>
+        </is>
+      </c>
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="38" t="inlineStr">
+        <is>
+          <t>Técnico SAT</t>
+        </is>
+      </c>
+      <c r="E17" s="38" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F17" s="39" t="n"/>
+      <c r="G17" s="39" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="36" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="37" t="inlineStr">
+        <is>
+          <t>Revisar el desgaste de las muelas del molinillo por kilos molidos (orientativo: planas 400-600 kg, cónicas 800-1.200 kg) y cambiarlas si toca</t>
+        </is>
+      </c>
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="38" t="inlineStr">
+        <is>
+          <t>Técnico SAT</t>
+        </is>
+      </c>
+      <c r="E18" s="38" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F18" s="39" t="n"/>
+      <c r="G18" s="39" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="41" t="inlineStr">
+        <is>
+          <t>Calibrar los termómetros y las sondas contra un patrón conocido (agua con hielo, 0 °C)</t>
+        </is>
+      </c>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="38" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E19" s="38" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F19" s="39" t="n"/>
+      <c r="G19" s="39" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ADMINISTRACIÓN Y SEGUROS</t>
+        </is>
+      </c>
+      <c r="B20" s="35" t="n"/>
+      <c r="C20" s="35" t="n"/>
+      <c r="D20" s="35" t="n"/>
+      <c r="E20" s="35" t="n"/>
+      <c r="F20" s="35" t="n"/>
+      <c r="G20" s="35" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="40" t="n">
+        <v>13</v>
+      </c>
+      <c r="B21" s="41" t="inlineStr">
+        <is>
+          <t>Revisar la póliza del local (continente, contenido y responsabilidad civil) y su fecha de vencimiento</t>
+        </is>
+      </c>
+      <c r="C21" s="38" t="n"/>
+      <c r="D21" s="38" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E21" s="38" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F21" s="39" t="n"/>
+      <c r="G21" s="39" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="36" t="n">
+        <v>14</v>
+      </c>
+      <c r="B22" s="37" t="inlineStr">
+        <is>
+          <t>Revisión del TPV y del software de facturación (requisitos antifraude / Verifactu)</t>
+        </is>
+      </c>
+      <c r="C22" s="38" t="n"/>
+      <c r="D22" s="38" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E22" s="38" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F22" s="39" t="n"/>
+      <c r="G22" s="39" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="40" t="n">
+        <v>15</v>
+      </c>
+      <c r="B23" s="41" t="inlineStr">
+        <is>
+          <t>Anotar la fecha de la próxima revisión de cada contrato y archivar el parte firmado</t>
+        </is>
+      </c>
+      <c r="C23" s="38" t="n"/>
+      <c r="D23" s="38" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E23" s="38" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="F23" s="39" t="n"/>
+      <c r="G23" s="39" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="42" t="n"/>
+      <c r="B24" s="43" t="n"/>
+      <c r="C24" s="38" t="n"/>
+      <c r="D24" s="38" t="n"/>
+      <c r="E24" s="38" t="n"/>
+      <c r="F24" s="39" t="n"/>
+      <c r="G24" s="39" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="42" t="n"/>
+      <c r="B25" s="43" t="n"/>
+      <c r="C25" s="38" t="n"/>
+      <c r="D25" s="38" t="n"/>
+      <c r="E25" s="38" t="n"/>
+      <c r="F25" s="39" t="n"/>
+      <c r="G25" s="39" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="42" t="n"/>
+      <c r="B26" s="43" t="n"/>
+      <c r="C26" s="38" t="n"/>
+      <c r="D26" s="38" t="n"/>
+      <c r="E26" s="38" t="n"/>
+      <c r="F26" s="39" t="n"/>
+      <c r="G26" s="39" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="42" t="n"/>
+      <c r="B27" s="43" t="n"/>
+      <c r="C27" s="38" t="n"/>
+      <c r="D27" s="38" t="n"/>
+      <c r="E27" s="38" t="n"/>
+      <c r="F27" s="39" t="n"/>
+      <c r="G27" s="39" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="42" t="n"/>
+      <c r="B28" s="43" t="n"/>
+      <c r="C28" s="38" t="n"/>
+      <c r="D28" s="38" t="n"/>
+      <c r="E28" s="38" t="n"/>
+      <c r="F28" s="39" t="n"/>
+      <c r="G28" s="39" t="n"/>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D30" s="28">
+        <f>COUNTIFS(B5:B28,"?*",F5:F28,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F30">
+        <f>COUNTIF(B5:B28,"?*")-COUNTIF(F5:F28,"N/A")</f>
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Firma encargado/a: _________________________    Hora: _________</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Cafetería / Brunch · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="9">
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A10:G10"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:G28">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F15 F16 F17 F18 F19 F21 F22 F23 F24 F25 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
